--- a/assets/template/Ingredient_template.xlsx
+++ b/assets/template/Ingredient_template.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="21">
   <si>
     <r>
       <rPr>
@@ -71,6 +71,9 @@
     </r>
   </si>
   <si>
+    <t>Verification Code</t>
+  </si>
+  <si>
     <t>Device Name</t>
   </si>
   <si>
@@ -92,6 +95,9 @@
     <t>Water</t>
   </si>
   <si>
+    <t>B1001061008</t>
+  </si>
+  <si>
     <t>XD-101</t>
   </si>
   <si>
@@ -105,6 +111,9 @@
   </si>
   <si>
     <t>Enter the name of the Ingredient.</t>
+  </si>
+  <si>
+    <t>Enter the barcode of the Ingredient.</t>
   </si>
   <si>
     <t>Enter the name of the scale used to weigh this ingredient.</t>
@@ -1252,17 +1261,17 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
-  <sheetFormatPr defaultColWidth="14.4285714285714" defaultRowHeight="15" customHeight="1" outlineLevelCol="4"/>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr defaultColWidth="14.4285714285714" defaultRowHeight="15" customHeight="1" outlineLevelRow="4" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="29" customWidth="1"/>
-    <col min="2" max="2" width="28.447619047619" customWidth="1"/>
-    <col min="3" max="3" width="48.6666666666667" customWidth="1"/>
-    <col min="4" max="4" width="43.1142857142857" customWidth="1"/>
-    <col min="5" max="5" width="46.8857142857143" customWidth="1"/>
+    <col min="2" max="3" width="28.447619047619" customWidth="1"/>
+    <col min="4" max="4" width="48.6666666666667" customWidth="1"/>
+    <col min="5" max="5" width="43.1142857142857" customWidth="1"/>
+    <col min="6" max="6" width="46.8857142857143" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="1:5">
+    <row r="1" customHeight="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1278,65 +1287,74 @@
       <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="2" customHeight="1" spans="1:5">
+    <row r="2" customHeight="1" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>7</v>
       </c>
     </row>
-    <row r="3" customHeight="1" spans="1:5">
+    <row r="3" customHeight="1" spans="1:6">
       <c r="A3" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="6" t="s">
         <v>9</v>
       </c>
+      <c r="C3" s="5" t="s">
+        <v>10</v>
+      </c>
       <c r="D3" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>13</v>
       </c>
     </row>
-    <row r="4" customHeight="1" spans="1:5">
+    <row r="4" customHeight="1" spans="1:6">
       <c r="A4" s="3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
-    <row r="5" customHeight="1" spans="1:1">
+    <row r="5" customHeight="1" spans="1:6">
       <c r="A5" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" customHeight="1" spans="3:3">
-      <c r="C9" s="4"/>
+        <v>20</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
